--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA309"/>
+  <dimension ref="A1:AA327"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -34341,6 +34341,1344 @@
         </is>
       </c>
     </row>
+    <row r="310">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>MM Liquor Wholesale</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr"/>
+      <c r="C310" s="2" t="inlineStr">
+        <is>
+          <t>168641</t>
+        </is>
+      </c>
+      <c r="D310" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E310" s="2" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="F310" s="2" t="inlineStr"/>
+      <c r="G310" s="2" t="inlineStr">
+        <is>
+          <t>453 Jules Street</t>
+        </is>
+      </c>
+      <c r="H310" s="2" t="inlineStr">
+        <is>
+          <t>2094</t>
+        </is>
+      </c>
+      <c r="I310" s="2" t="inlineStr">
+        <is>
+          <t>https://mmliquor.co.za</t>
+        </is>
+      </c>
+      <c r="J310" s="2" t="inlineStr"/>
+      <c r="K310" s="2" t="inlineStr"/>
+      <c r="L310" s="2" t="inlineStr"/>
+      <c r="M310" s="2" t="inlineStr"/>
+      <c r="N310" s="2" t="inlineStr">
+        <is>
+          <t>info@mmliquor.co.za</t>
+        </is>
+      </c>
+      <c r="O310" s="2" t="inlineStr"/>
+      <c r="P310" s="2" t="inlineStr"/>
+      <c r="Q310" s="2" t="inlineStr"/>
+      <c r="R310" s="2" t="inlineStr"/>
+      <c r="S310" s="2" t="inlineStr"/>
+      <c r="T310" s="2" t="inlineStr"/>
+      <c r="U310" s="2" t="inlineStr"/>
+      <c r="V310" s="2" t="inlineStr"/>
+      <c r="W310" s="2" t="inlineStr"/>
+      <c r="X310" s="2" t="inlineStr"/>
+      <c r="Y310" s="2" t="inlineStr"/>
+      <c r="Z310" s="2" t="inlineStr"/>
+      <c r="AA310" s="2" t="inlineStr"/>
+    </row>
+    <row r="311">
+      <c r="A311" s="2" t="inlineStr">
+        <is>
+          <t>Nationwide Liquor Distribution</t>
+        </is>
+      </c>
+      <c r="B311" s="2" t="inlineStr"/>
+      <c r="C311" s="2" t="inlineStr">
+        <is>
+          <t>168640</t>
+        </is>
+      </c>
+      <c r="D311" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E311" s="2" t="inlineStr">
+        <is>
+          <t>Heriotdale</t>
+        </is>
+      </c>
+      <c r="F311" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng</t>
+        </is>
+      </c>
+      <c r="G311" s="2" t="inlineStr">
+        <is>
+          <t>15 Hyser St</t>
+        </is>
+      </c>
+      <c r="H311" s="2" t="inlineStr"/>
+      <c r="I311" s="2" t="inlineStr">
+        <is>
+          <t>https://nldist.co.za</t>
+        </is>
+      </c>
+      <c r="J311" s="2" t="inlineStr"/>
+      <c r="K311" s="2" t="inlineStr"/>
+      <c r="L311" s="2" t="inlineStr"/>
+      <c r="M311" s="2" t="inlineStr"/>
+      <c r="N311" s="2" t="inlineStr">
+        <is>
+          <t>info@nldist.co.za</t>
+        </is>
+      </c>
+      <c r="O311" s="2" t="inlineStr"/>
+      <c r="P311" s="2" t="inlineStr"/>
+      <c r="Q311" s="2" t="inlineStr"/>
+      <c r="R311" s="2" t="inlineStr"/>
+      <c r="S311" s="2" t="inlineStr"/>
+      <c r="T311" s="2" t="inlineStr"/>
+      <c r="U311" s="2" t="inlineStr"/>
+      <c r="V311" s="2" t="inlineStr"/>
+      <c r="W311" s="2" t="inlineStr"/>
+      <c r="X311" s="2" t="inlineStr"/>
+      <c r="Y311" s="2" t="inlineStr"/>
+      <c r="Z311" s="2" t="inlineStr"/>
+      <c r="AA311" s="2" t="inlineStr"/>
+    </row>
+    <row r="312">
+      <c r="A312" s="2" t="inlineStr">
+        <is>
+          <t>The Wine Shop Cape Town</t>
+        </is>
+      </c>
+      <c r="B312" s="2" t="inlineStr"/>
+      <c r="C312" s="2" t="inlineStr">
+        <is>
+          <t>168639</t>
+        </is>
+      </c>
+      <c r="D312" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E312" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F312" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G312" s="2" t="inlineStr">
+        <is>
+          <t>199 Loop Street, Shop 2 Graphic Centre</t>
+        </is>
+      </c>
+      <c r="H312" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I312" s="2" t="inlineStr">
+        <is>
+          <t>https://thewineshopcapetown.co.za</t>
+        </is>
+      </c>
+      <c r="J312" s="2" t="inlineStr"/>
+      <c r="K312" s="2" t="inlineStr"/>
+      <c r="L312" s="2" t="inlineStr"/>
+      <c r="M312" s="2" t="inlineStr"/>
+      <c r="N312" s="2" t="inlineStr">
+        <is>
+          <t>info@thewineshopcapetown.co.za</t>
+        </is>
+      </c>
+      <c r="O312" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 462 6385</t>
+        </is>
+      </c>
+      <c r="P312" s="2" t="inlineStr"/>
+      <c r="Q312" s="2" t="inlineStr"/>
+      <c r="R312" s="2" t="inlineStr"/>
+      <c r="S312" s="2" t="inlineStr"/>
+      <c r="T312" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/rs_thewineshop/?hl=en</t>
+        </is>
+      </c>
+      <c r="U312" s="2" t="inlineStr"/>
+      <c r="V312" s="2" t="inlineStr"/>
+      <c r="W312" s="2" t="inlineStr"/>
+      <c r="X312" s="2" t="inlineStr"/>
+      <c r="Y312" s="2" t="inlineStr"/>
+      <c r="Z312" s="2" t="inlineStr"/>
+      <c r="AA312" s="2" t="inlineStr"/>
+    </row>
+    <row r="313">
+      <c r="A313" s="2" t="inlineStr">
+        <is>
+          <t>Whisky Emporium</t>
+        </is>
+      </c>
+      <c r="B313" s="2" t="inlineStr"/>
+      <c r="C313" s="2" t="inlineStr">
+        <is>
+          <t>168638</t>
+        </is>
+      </c>
+      <c r="D313" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E313" s="2" t="inlineStr">
+        <is>
+          <t>Pretoria</t>
+        </is>
+      </c>
+      <c r="F313" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng</t>
+        </is>
+      </c>
+      <c r="G313" s="2" t="inlineStr">
+        <is>
+          <t>Shop G215, Menlyn Park Shopping Centre, Corner Atterbury Road, Lois Ave</t>
+        </is>
+      </c>
+      <c r="H313" s="2" t="inlineStr">
+        <is>
+          <t>0063</t>
+        </is>
+      </c>
+      <c r="I313" s="2" t="inlineStr">
+        <is>
+          <t>https://whiskyemporium.com</t>
+        </is>
+      </c>
+      <c r="J313" s="2" t="inlineStr"/>
+      <c r="K313" s="2" t="inlineStr"/>
+      <c r="L313" s="2" t="inlineStr"/>
+      <c r="M313" s="2" t="inlineStr"/>
+      <c r="N313" s="2" t="inlineStr">
+        <is>
+          <t>menlyn@whiskyemporium.co.za</t>
+        </is>
+      </c>
+      <c r="O313" s="2" t="inlineStr"/>
+      <c r="P313" s="2" t="inlineStr"/>
+      <c r="Q313" s="2" t="inlineStr"/>
+      <c r="R313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/whisky-emporium/</t>
+        </is>
+      </c>
+      <c r="S313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/LCWhiskyEmporium/</t>
+        </is>
+      </c>
+      <c r="T313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/whisky_emporium/</t>
+        </is>
+      </c>
+      <c r="U313" s="2" t="inlineStr"/>
+      <c r="V313" s="2" t="inlineStr"/>
+      <c r="W313" s="2" t="inlineStr">
+        <is>
+          <t>Norbert Martins</t>
+        </is>
+      </c>
+      <c r="X313" s="2" t="inlineStr">
+        <is>
+          <t>Founder</t>
+        </is>
+      </c>
+      <c r="Y313" s="2" t="inlineStr"/>
+      <c r="Z313" s="2" t="inlineStr"/>
+      <c r="AA313" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/norbert-martins/</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" s="2" t="inlineStr">
+        <is>
+          <t>Bx Wine Shop &amp; Bar</t>
+        </is>
+      </c>
+      <c r="B314" s="2" t="inlineStr"/>
+      <c r="C314" s="2" t="inlineStr">
+        <is>
+          <t>168637</t>
+        </is>
+      </c>
+      <c r="D314" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E314" s="2" t="inlineStr">
+        <is>
+          <t>Sandton</t>
+        </is>
+      </c>
+      <c r="F314" s="2" t="inlineStr"/>
+      <c r="G314" s="2" t="inlineStr">
+        <is>
+          <t>129 Rivonia Road</t>
+        </is>
+      </c>
+      <c r="H314" s="2" t="inlineStr">
+        <is>
+          <t>2196</t>
+        </is>
+      </c>
+      <c r="I314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.bxwine.co.za</t>
+        </is>
+      </c>
+      <c r="J314" s="2" t="inlineStr"/>
+      <c r="K314" s="2" t="inlineStr"/>
+      <c r="L314" s="2" t="inlineStr"/>
+      <c r="M314" s="2" t="inlineStr"/>
+      <c r="N314" s="2" t="inlineStr">
+        <is>
+          <t>info@bxwine.co.za</t>
+        </is>
+      </c>
+      <c r="O314" s="2" t="inlineStr"/>
+      <c r="P314" s="2" t="inlineStr"/>
+      <c r="Q314" s="2" t="inlineStr"/>
+      <c r="R314" s="2" t="inlineStr"/>
+      <c r="S314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Bx-Wine-Bar-Shop-61581232665890/</t>
+        </is>
+      </c>
+      <c r="T314" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/bxwineshop/</t>
+        </is>
+      </c>
+      <c r="U314" s="2" t="inlineStr"/>
+      <c r="V314" s="2" t="inlineStr"/>
+      <c r="W314" s="2" t="inlineStr"/>
+      <c r="X314" s="2" t="inlineStr"/>
+      <c r="Y314" s="2" t="inlineStr"/>
+      <c r="Z314" s="2" t="inlineStr"/>
+      <c r="AA314" s="2" t="inlineStr"/>
+    </row>
+    <row r="315">
+      <c r="A315" s="2" t="inlineStr">
+        <is>
+          <t>La Verne Wine Boutique</t>
+        </is>
+      </c>
+      <c r="B315" s="2" t="inlineStr"/>
+      <c r="C315" s="2" t="inlineStr">
+        <is>
+          <t>168636</t>
+        </is>
+      </c>
+      <c r="D315" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E315" s="2" t="inlineStr">
+        <is>
+          <t>Robertson</t>
+        </is>
+      </c>
+      <c r="F315" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G315" s="2" t="inlineStr">
+        <is>
+          <t>1 Voortrekker Road</t>
+        </is>
+      </c>
+      <c r="H315" s="2" t="inlineStr">
+        <is>
+          <t>6705</t>
+        </is>
+      </c>
+      <c r="I315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.lavernewines.co.za</t>
+        </is>
+      </c>
+      <c r="J315" s="2" t="inlineStr"/>
+      <c r="K315" s="2" t="inlineStr"/>
+      <c r="L315" s="2" t="inlineStr"/>
+      <c r="M315" s="2" t="inlineStr"/>
+      <c r="N315" s="2" t="inlineStr">
+        <is>
+          <t>info@lavernewines.co.za</t>
+        </is>
+      </c>
+      <c r="O315" s="2" t="inlineStr">
+        <is>
+          <t>+27 23 626 4314</t>
+        </is>
+      </c>
+      <c r="P315" s="2" t="inlineStr"/>
+      <c r="Q315" s="2" t="inlineStr"/>
+      <c r="R315" s="2" t="inlineStr"/>
+      <c r="S315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Lavernewineboutique</t>
+        </is>
+      </c>
+      <c r="T315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/lavernewineboutique/</t>
+        </is>
+      </c>
+      <c r="U315" s="2" t="inlineStr"/>
+      <c r="V315" s="2" t="inlineStr"/>
+      <c r="W315" s="2" t="inlineStr">
+        <is>
+          <t>Franzelle Paulsen</t>
+        </is>
+      </c>
+      <c r="X315" s="2" t="inlineStr">
+        <is>
+          <t>Sales and Marketing Manager</t>
+        </is>
+      </c>
+      <c r="Y315" s="2" t="inlineStr"/>
+      <c r="Z315" s="2" t="inlineStr"/>
+      <c r="AA315" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/franzelle-paulsen-895b4597/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" s="2" t="inlineStr">
+        <is>
+          <t>Grapevine Blue Bottle Liquors</t>
+        </is>
+      </c>
+      <c r="B316" s="2" t="inlineStr"/>
+      <c r="C316" s="2" t="inlineStr">
+        <is>
+          <t>168635</t>
+        </is>
+      </c>
+      <c r="D316" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E316" s="2" t="inlineStr">
+        <is>
+          <t>Robertson</t>
+        </is>
+      </c>
+      <c r="F316" s="2" t="inlineStr">
+        <is>
+          <t>Western Australia</t>
+        </is>
+      </c>
+      <c r="G316" s="2" t="inlineStr">
+        <is>
+          <t>58 Barry Street</t>
+        </is>
+      </c>
+      <c r="H316" s="2" t="inlineStr">
+        <is>
+          <t>6708</t>
+        </is>
+      </c>
+      <c r="I316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.grapevineliquors.co.za</t>
+        </is>
+      </c>
+      <c r="J316" s="2" t="inlineStr"/>
+      <c r="K316" s="2" t="inlineStr"/>
+      <c r="L316" s="2" t="inlineStr"/>
+      <c r="M316" s="2" t="inlineStr"/>
+      <c r="N316" s="2" t="inlineStr">
+        <is>
+          <t>jurgens@grapevineliquors.co.za</t>
+        </is>
+      </c>
+      <c r="O316" s="2" t="inlineStr">
+        <is>
+          <t>+27 23 626 3451</t>
+        </is>
+      </c>
+      <c r="P316" s="2" t="inlineStr"/>
+      <c r="Q316" s="2" t="inlineStr"/>
+      <c r="R316" s="2" t="inlineStr"/>
+      <c r="S316" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/grapevineblue/</t>
+        </is>
+      </c>
+      <c r="T316" s="2" t="inlineStr"/>
+      <c r="U316" s="2" t="inlineStr"/>
+      <c r="V316" s="2" t="inlineStr"/>
+      <c r="W316" s="2" t="inlineStr"/>
+      <c r="X316" s="2" t="inlineStr"/>
+      <c r="Y316" s="2" t="inlineStr"/>
+      <c r="Z316" s="2" t="inlineStr"/>
+      <c r="AA316" s="2" t="inlineStr"/>
+    </row>
+    <row r="317">
+      <c r="A317" s="2" t="inlineStr">
+        <is>
+          <t>Brand Republic</t>
+        </is>
+      </c>
+      <c r="B317" s="2" t="inlineStr"/>
+      <c r="C317" s="2" t="inlineStr">
+        <is>
+          <t>168634</t>
+        </is>
+      </c>
+      <c r="D317" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E317" s="2" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="F317" s="2" t="inlineStr"/>
+      <c r="G317" s="2" t="inlineStr">
+        <is>
+          <t>12 Buitekant St</t>
+        </is>
+      </c>
+      <c r="H317" s="2" t="inlineStr">
+        <is>
+          <t>6529</t>
+        </is>
+      </c>
+      <c r="I317" s="2" t="inlineStr">
+        <is>
+          <t>https://www.brand-republic.co.za</t>
+        </is>
+      </c>
+      <c r="J317" s="2" t="inlineStr"/>
+      <c r="K317" s="2" t="inlineStr"/>
+      <c r="L317" s="2" t="inlineStr"/>
+      <c r="M317" s="2" t="inlineStr"/>
+      <c r="N317" s="2" t="inlineStr">
+        <is>
+          <t>office@brand-republic.co.za</t>
+        </is>
+      </c>
+      <c r="O317" s="2" t="inlineStr"/>
+      <c r="P317" s="2" t="inlineStr"/>
+      <c r="Q317" s="2" t="inlineStr"/>
+      <c r="R317" s="2" t="inlineStr"/>
+      <c r="S317" s="2" t="inlineStr"/>
+      <c r="T317" s="2" t="inlineStr"/>
+      <c r="U317" s="2" t="inlineStr"/>
+      <c r="V317" s="2" t="inlineStr"/>
+      <c r="W317" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Juan </t>
+        </is>
+      </c>
+      <c r="X317" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y317" s="2" t="inlineStr"/>
+      <c r="Z317" s="2" t="inlineStr"/>
+      <c r="AA317" s="2" t="inlineStr"/>
+    </row>
+    <row r="318">
+      <c r="A318" s="2" t="inlineStr">
+        <is>
+          <t>Afrovino (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B318" s="2" t="inlineStr"/>
+      <c r="C318" s="2" t="inlineStr">
+        <is>
+          <t>168633</t>
+        </is>
+      </c>
+      <c r="D318" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E318" s="2" t="inlineStr">
+        <is>
+          <t>Mbombela</t>
+        </is>
+      </c>
+      <c r="F318" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga</t>
+        </is>
+      </c>
+      <c r="G318" s="2" t="inlineStr">
+        <is>
+          <t>Promenade Shopping Centre</t>
+        </is>
+      </c>
+      <c r="H318" s="2" t="inlineStr"/>
+      <c r="I318" s="2" t="inlineStr">
+        <is>
+          <t>https://afrovino.com</t>
+        </is>
+      </c>
+      <c r="J318" s="2" t="inlineStr"/>
+      <c r="K318" s="2" t="inlineStr"/>
+      <c r="L318" s="2" t="inlineStr"/>
+      <c r="M318" s="2" t="inlineStr"/>
+      <c r="N318" s="2" t="inlineStr">
+        <is>
+          <t>sales@afrovino.com</t>
+        </is>
+      </c>
+      <c r="O318" s="2" t="inlineStr"/>
+      <c r="P318" s="2" t="inlineStr"/>
+      <c r="Q318" s="2" t="inlineStr"/>
+      <c r="R318" s="2" t="inlineStr"/>
+      <c r="S318" s="2" t="inlineStr"/>
+      <c r="T318" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/kunye.wines</t>
+        </is>
+      </c>
+      <c r="U318" s="2" t="inlineStr"/>
+      <c r="V318" s="2" t="inlineStr"/>
+      <c r="W318" s="2" t="inlineStr">
+        <is>
+          <t>Chenjerai Gumbo</t>
+        </is>
+      </c>
+      <c r="X318" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y318" s="2" t="inlineStr"/>
+      <c r="Z318" s="2" t="inlineStr"/>
+      <c r="AA318" s="2" t="inlineStr"/>
+    </row>
+    <row r="319">
+      <c r="A319" s="2" t="inlineStr">
+        <is>
+          <t>Afrovino (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B319" s="2" t="inlineStr"/>
+      <c r="C319" s="2" t="inlineStr">
+        <is>
+          <t>168633</t>
+        </is>
+      </c>
+      <c r="D319" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E319" s="2" t="inlineStr">
+        <is>
+          <t>Mbombela</t>
+        </is>
+      </c>
+      <c r="F319" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga</t>
+        </is>
+      </c>
+      <c r="G319" s="2" t="inlineStr">
+        <is>
+          <t>Promenade Shopping Centre</t>
+        </is>
+      </c>
+      <c r="H319" s="2" t="inlineStr"/>
+      <c r="I319" s="2" t="inlineStr">
+        <is>
+          <t>https://afrovino.com</t>
+        </is>
+      </c>
+      <c r="J319" s="2" t="inlineStr"/>
+      <c r="K319" s="2" t="inlineStr"/>
+      <c r="L319" s="2" t="inlineStr"/>
+      <c r="M319" s="2" t="inlineStr"/>
+      <c r="N319" s="2" t="inlineStr">
+        <is>
+          <t>sales@afrovino.com</t>
+        </is>
+      </c>
+      <c r="O319" s="2" t="inlineStr"/>
+      <c r="P319" s="2" t="inlineStr"/>
+      <c r="Q319" s="2" t="inlineStr"/>
+      <c r="R319" s="2" t="inlineStr"/>
+      <c r="S319" s="2" t="inlineStr"/>
+      <c r="T319" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/kunye.wines</t>
+        </is>
+      </c>
+      <c r="U319" s="2" t="inlineStr"/>
+      <c r="V319" s="2" t="inlineStr"/>
+      <c r="W319" s="2" t="inlineStr">
+        <is>
+          <t>Zweli Mabuza</t>
+        </is>
+      </c>
+      <c r="X319" s="2" t="inlineStr">
+        <is>
+          <t>Operations Director</t>
+        </is>
+      </c>
+      <c r="Y319" s="2" t="inlineStr"/>
+      <c r="Z319" s="2" t="inlineStr"/>
+      <c r="AA319" s="2" t="inlineStr"/>
+    </row>
+    <row r="320">
+      <c r="A320" s="2" t="inlineStr">
+        <is>
+          <t>Afrovino (Pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B320" s="2" t="inlineStr"/>
+      <c r="C320" s="2" t="inlineStr">
+        <is>
+          <t>168633</t>
+        </is>
+      </c>
+      <c r="D320" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E320" s="2" t="inlineStr">
+        <is>
+          <t>Mbombela</t>
+        </is>
+      </c>
+      <c r="F320" s="2" t="inlineStr">
+        <is>
+          <t>Mpumalanga</t>
+        </is>
+      </c>
+      <c r="G320" s="2" t="inlineStr">
+        <is>
+          <t>Promenade Shopping Centre</t>
+        </is>
+      </c>
+      <c r="H320" s="2" t="inlineStr"/>
+      <c r="I320" s="2" t="inlineStr">
+        <is>
+          <t>https://afrovino.com</t>
+        </is>
+      </c>
+      <c r="J320" s="2" t="inlineStr"/>
+      <c r="K320" s="2" t="inlineStr"/>
+      <c r="L320" s="2" t="inlineStr"/>
+      <c r="M320" s="2" t="inlineStr"/>
+      <c r="N320" s="2" t="inlineStr">
+        <is>
+          <t>sales@afrovino.com</t>
+        </is>
+      </c>
+      <c r="O320" s="2" t="inlineStr"/>
+      <c r="P320" s="2" t="inlineStr"/>
+      <c r="Q320" s="2" t="inlineStr"/>
+      <c r="R320" s="2" t="inlineStr"/>
+      <c r="S320" s="2" t="inlineStr"/>
+      <c r="T320" s="2" t="inlineStr">
+        <is>
+          <t>https://instagram.com/kunye.wines</t>
+        </is>
+      </c>
+      <c r="U320" s="2" t="inlineStr"/>
+      <c r="V320" s="2" t="inlineStr"/>
+      <c r="W320" s="2" t="inlineStr">
+        <is>
+          <t>Mhlonishwa Gamedze</t>
+        </is>
+      </c>
+      <c r="X320" s="2" t="inlineStr">
+        <is>
+          <t>Sales Director</t>
+        </is>
+      </c>
+      <c r="Y320" s="2" t="inlineStr"/>
+      <c r="Z320" s="2" t="inlineStr"/>
+      <c r="AA320" s="2" t="inlineStr"/>
+    </row>
+    <row r="321">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>NLR Wines</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr"/>
+      <c r="C321" s="2" t="inlineStr">
+        <is>
+          <t>168632</t>
+        </is>
+      </c>
+      <c r="D321" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E321" s="2" t="inlineStr">
+        <is>
+          <t>George</t>
+        </is>
+      </c>
+      <c r="F321" s="2" t="inlineStr"/>
+      <c r="G321" s="2" t="inlineStr">
+        <is>
+          <t>12 Ring Rd, George Industria</t>
+        </is>
+      </c>
+      <c r="H321" s="2" t="inlineStr">
+        <is>
+          <t>6536</t>
+        </is>
+      </c>
+      <c r="I321" s="2" t="inlineStr">
+        <is>
+          <t>https://nlrwines.co.za, https://wineonroute.co.za</t>
+        </is>
+      </c>
+      <c r="J321" s="2" t="inlineStr"/>
+      <c r="K321" s="2" t="inlineStr"/>
+      <c r="L321" s="2" t="inlineStr"/>
+      <c r="M321" s="2" t="inlineStr"/>
+      <c r="N321" s="2" t="inlineStr">
+        <is>
+          <t>orders@nlrwines.co.za</t>
+        </is>
+      </c>
+      <c r="O321" s="2" t="inlineStr">
+        <is>
+          <t>+27 44 873 5641</t>
+        </is>
+      </c>
+      <c r="P321" s="2" t="inlineStr"/>
+      <c r="Q321" s="2" t="inlineStr"/>
+      <c r="R321" s="2" t="inlineStr"/>
+      <c r="S321" s="2" t="inlineStr"/>
+      <c r="T321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/nlrwine/</t>
+        </is>
+      </c>
+      <c r="U321" s="2" t="inlineStr"/>
+      <c r="V321" s="2" t="inlineStr"/>
+      <c r="W321" s="2" t="inlineStr">
+        <is>
+          <t>Nell-Marie Le Roux</t>
+        </is>
+      </c>
+      <c r="X321" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y321" s="2" t="inlineStr"/>
+      <c r="Z321" s="2" t="inlineStr"/>
+      <c r="AA321" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/nell-marie-le-roux-9a22651b5/</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" s="2" t="inlineStr">
+        <is>
+          <t>DMT Logistics</t>
+        </is>
+      </c>
+      <c r="B322" s="2" t="inlineStr"/>
+      <c r="C322" s="2" t="inlineStr">
+        <is>
+          <t>168630</t>
+        </is>
+      </c>
+      <c r="D322" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E322" s="2" t="inlineStr">
+        <is>
+          <t>Port Elizabeth</t>
+        </is>
+      </c>
+      <c r="F322" s="2" t="inlineStr">
+        <is>
+          <t>Eastern Cape</t>
+        </is>
+      </c>
+      <c r="G322" s="2" t="inlineStr">
+        <is>
+          <t>95 Martin Street</t>
+        </is>
+      </c>
+      <c r="H322" s="2" t="inlineStr">
+        <is>
+          <t>6001</t>
+        </is>
+      </c>
+      <c r="I322" s="2" t="inlineStr">
+        <is>
+          <t>https://dmtlogistics.co.za</t>
+        </is>
+      </c>
+      <c r="J322" s="2" t="inlineStr"/>
+      <c r="K322" s="2" t="inlineStr"/>
+      <c r="L322" s="2" t="inlineStr"/>
+      <c r="M322" s="2" t="inlineStr"/>
+      <c r="N322" s="2" t="inlineStr">
+        <is>
+          <t>admin@dmtlogistics.co.za</t>
+        </is>
+      </c>
+      <c r="O322" s="2" t="inlineStr">
+        <is>
+          <t>+27 41 451 0266</t>
+        </is>
+      </c>
+      <c r="P322" s="2" t="inlineStr"/>
+      <c r="Q322" s="2" t="inlineStr"/>
+      <c r="R322" s="2" t="inlineStr"/>
+      <c r="S322" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/dmtlogisticsza</t>
+        </is>
+      </c>
+      <c r="T322" s="2" t="inlineStr"/>
+      <c r="U322" s="2" t="inlineStr"/>
+      <c r="V322" s="2" t="inlineStr"/>
+      <c r="W322" s="2" t="inlineStr"/>
+      <c r="X322" s="2" t="inlineStr"/>
+      <c r="Y322" s="2" t="inlineStr"/>
+      <c r="Z322" s="2" t="inlineStr"/>
+      <c r="AA322" s="2" t="inlineStr"/>
+    </row>
+    <row r="323">
+      <c r="A323" s="2" t="inlineStr">
+        <is>
+          <t>Sam's Liquor Group</t>
+        </is>
+      </c>
+      <c r="B323" s="2" t="inlineStr"/>
+      <c r="C323" s="2" t="inlineStr">
+        <is>
+          <t>168629</t>
+        </is>
+      </c>
+      <c r="D323" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E323" s="2" t="inlineStr">
+        <is>
+          <t>Germiston</t>
+        </is>
+      </c>
+      <c r="F323" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng</t>
+        </is>
+      </c>
+      <c r="G323" s="2" t="inlineStr">
+        <is>
+          <t>Keranatela St</t>
+        </is>
+      </c>
+      <c r="H323" s="2" t="inlineStr">
+        <is>
+          <t>1401</t>
+        </is>
+      </c>
+      <c r="I323" s="2" t="inlineStr">
+        <is>
+          <t>https://samsliquor.co.za</t>
+        </is>
+      </c>
+      <c r="J323" s="2" t="inlineStr"/>
+      <c r="K323" s="2" t="inlineStr"/>
+      <c r="L323" s="2" t="inlineStr"/>
+      <c r="M323" s="2" t="inlineStr"/>
+      <c r="N323" s="2" t="inlineStr">
+        <is>
+          <t>info@samsliquor.co.za</t>
+        </is>
+      </c>
+      <c r="O323" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 905 4619</t>
+        </is>
+      </c>
+      <c r="P323" s="2" t="inlineStr"/>
+      <c r="Q323" s="2" t="inlineStr"/>
+      <c r="R323" s="2" t="inlineStr"/>
+      <c r="S323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/samsliqours</t>
+        </is>
+      </c>
+      <c r="T323" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sams.liquorstore</t>
+        </is>
+      </c>
+      <c r="U323" s="2" t="inlineStr"/>
+      <c r="V323" s="2" t="inlineStr"/>
+      <c r="W323" s="2" t="inlineStr"/>
+      <c r="X323" s="2" t="inlineStr"/>
+      <c r="Y323" s="2" t="inlineStr"/>
+      <c r="Z323" s="2" t="inlineStr"/>
+      <c r="AA323" s="2" t="inlineStr"/>
+    </row>
+    <row r="324">
+      <c r="A324" s="2" t="inlineStr">
+        <is>
+          <t>Provimar Ship Suppliers CC</t>
+        </is>
+      </c>
+      <c r="B324" s="2" t="inlineStr"/>
+      <c r="C324" s="2" t="inlineStr">
+        <is>
+          <t>168628</t>
+        </is>
+      </c>
+      <c r="D324" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E324" s="2" t="inlineStr">
+        <is>
+          <t>Durban</t>
+        </is>
+      </c>
+      <c r="F324" s="2" t="inlineStr">
+        <is>
+          <t>KwaZulu-Natal</t>
+        </is>
+      </c>
+      <c r="G324" s="2" t="inlineStr">
+        <is>
+          <t>360 Magwaza Maphalala St</t>
+        </is>
+      </c>
+      <c r="H324" s="2" t="inlineStr">
+        <is>
+          <t>4013</t>
+        </is>
+      </c>
+      <c r="I324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.provimar.co.za</t>
+        </is>
+      </c>
+      <c r="J324" s="2" t="inlineStr"/>
+      <c r="K324" s="2" t="inlineStr"/>
+      <c r="L324" s="2" t="inlineStr"/>
+      <c r="M324" s="2" t="inlineStr"/>
+      <c r="N324" s="2" t="inlineStr">
+        <is>
+          <t>sales@provimar.co.za</t>
+        </is>
+      </c>
+      <c r="O324" s="2" t="inlineStr">
+        <is>
+          <t>+27 31 304 9411</t>
+        </is>
+      </c>
+      <c r="P324" s="2" t="inlineStr"/>
+      <c r="Q324" s="2" t="inlineStr"/>
+      <c r="R324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ricardo-manuel-garces-39677928/</t>
+        </is>
+      </c>
+      <c r="S324" s="2" t="inlineStr"/>
+      <c r="T324" s="2" t="inlineStr"/>
+      <c r="U324" s="2" t="inlineStr"/>
+      <c r="V324" s="2" t="inlineStr"/>
+      <c r="W324" s="2" t="inlineStr">
+        <is>
+          <t>Ricardo Manuel Garces</t>
+        </is>
+      </c>
+      <c r="X324" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y324" s="2" t="inlineStr"/>
+      <c r="Z324" s="2" t="inlineStr"/>
+      <c r="AA324" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/ricardo-manuel-garces-39677928/</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" s="2" t="inlineStr">
+        <is>
+          <t>Cape Wine Group</t>
+        </is>
+      </c>
+      <c r="B325" s="2" t="inlineStr"/>
+      <c r="C325" s="2" t="inlineStr">
+        <is>
+          <t>168627</t>
+        </is>
+      </c>
+      <c r="D325" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E325" s="2" t="inlineStr">
+        <is>
+          <t>Somerset West</t>
+        </is>
+      </c>
+      <c r="F325" s="2" t="inlineStr"/>
+      <c r="G325" s="2" t="inlineStr">
+        <is>
+          <t>10 Blend Crescent</t>
+        </is>
+      </c>
+      <c r="H325" s="2" t="inlineStr"/>
+      <c r="I325" s="2" t="inlineStr">
+        <is>
+          <t>https://capewinegroup.co.za</t>
+        </is>
+      </c>
+      <c r="J325" s="2" t="inlineStr"/>
+      <c r="K325" s="2" t="inlineStr"/>
+      <c r="L325" s="2" t="inlineStr"/>
+      <c r="M325" s="2" t="inlineStr"/>
+      <c r="N325" s="2" t="inlineStr">
+        <is>
+          <t>sales-orders@capewinegroup.co.za</t>
+        </is>
+      </c>
+      <c r="O325" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 300 3157</t>
+        </is>
+      </c>
+      <c r="P325" s="2" t="inlineStr"/>
+      <c r="Q325" s="2" t="inlineStr"/>
+      <c r="R325" s="2" t="inlineStr"/>
+      <c r="S325" s="2" t="inlineStr"/>
+      <c r="T325" s="2" t="inlineStr"/>
+      <c r="U325" s="2" t="inlineStr"/>
+      <c r="V325" s="2" t="inlineStr"/>
+      <c r="W325" s="2" t="inlineStr">
+        <is>
+          <t>Cornel Nieuwoudt</t>
+        </is>
+      </c>
+      <c r="X325" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Commercial Manager </t>
+        </is>
+      </c>
+      <c r="Y325" s="2" t="inlineStr"/>
+      <c r="Z325" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA325" s="2" t="inlineStr"/>
+    </row>
+    <row r="326">
+      <c r="A326" s="2" t="inlineStr">
+        <is>
+          <t>Cape Wine Group</t>
+        </is>
+      </c>
+      <c r="B326" s="2" t="inlineStr"/>
+      <c r="C326" s="2" t="inlineStr">
+        <is>
+          <t>168627</t>
+        </is>
+      </c>
+      <c r="D326" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E326" s="2" t="inlineStr">
+        <is>
+          <t>Somerset West</t>
+        </is>
+      </c>
+      <c r="F326" s="2" t="inlineStr"/>
+      <c r="G326" s="2" t="inlineStr">
+        <is>
+          <t>10 Blend Crescent</t>
+        </is>
+      </c>
+      <c r="H326" s="2" t="inlineStr"/>
+      <c r="I326" s="2" t="inlineStr">
+        <is>
+          <t>https://capewinegroup.co.za</t>
+        </is>
+      </c>
+      <c r="J326" s="2" t="inlineStr"/>
+      <c r="K326" s="2" t="inlineStr"/>
+      <c r="L326" s="2" t="inlineStr"/>
+      <c r="M326" s="2" t="inlineStr"/>
+      <c r="N326" s="2" t="inlineStr">
+        <is>
+          <t>sales-orders@capewinegroup.co.za</t>
+        </is>
+      </c>
+      <c r="O326" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 300 3157</t>
+        </is>
+      </c>
+      <c r="P326" s="2" t="inlineStr"/>
+      <c r="Q326" s="2" t="inlineStr"/>
+      <c r="R326" s="2" t="inlineStr"/>
+      <c r="S326" s="2" t="inlineStr"/>
+      <c r="T326" s="2" t="inlineStr"/>
+      <c r="U326" s="2" t="inlineStr"/>
+      <c r="V326" s="2" t="inlineStr"/>
+      <c r="W326" s="2" t="inlineStr">
+        <is>
+          <t>Jacques Steenkamp</t>
+        </is>
+      </c>
+      <c r="X326" s="2" t="inlineStr">
+        <is>
+          <t>Managing Director</t>
+        </is>
+      </c>
+      <c r="Y326" s="2" t="inlineStr"/>
+      <c r="Z326" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA326" s="2" t="inlineStr"/>
+    </row>
+    <row r="327">
+      <c r="A327" s="2" t="inlineStr">
+        <is>
+          <t>Cape Wine Group</t>
+        </is>
+      </c>
+      <c r="B327" s="2" t="inlineStr"/>
+      <c r="C327" s="2" t="inlineStr">
+        <is>
+          <t>168627</t>
+        </is>
+      </c>
+      <c r="D327" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E327" s="2" t="inlineStr">
+        <is>
+          <t>Somerset West</t>
+        </is>
+      </c>
+      <c r="F327" s="2" t="inlineStr"/>
+      <c r="G327" s="2" t="inlineStr">
+        <is>
+          <t>10 Blend Crescent</t>
+        </is>
+      </c>
+      <c r="H327" s="2" t="inlineStr"/>
+      <c r="I327" s="2" t="inlineStr">
+        <is>
+          <t>https://capewinegroup.co.za</t>
+        </is>
+      </c>
+      <c r="J327" s="2" t="inlineStr"/>
+      <c r="K327" s="2" t="inlineStr"/>
+      <c r="L327" s="2" t="inlineStr"/>
+      <c r="M327" s="2" t="inlineStr"/>
+      <c r="N327" s="2" t="inlineStr">
+        <is>
+          <t>sales-orders@capewinegroup.co.za</t>
+        </is>
+      </c>
+      <c r="O327" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 300 3157</t>
+        </is>
+      </c>
+      <c r="P327" s="2" t="inlineStr"/>
+      <c r="Q327" s="2" t="inlineStr"/>
+      <c r="R327" s="2" t="inlineStr"/>
+      <c r="S327" s="2" t="inlineStr"/>
+      <c r="T327" s="2" t="inlineStr"/>
+      <c r="U327" s="2" t="inlineStr"/>
+      <c r="V327" s="2" t="inlineStr"/>
+      <c r="W327" s="2" t="inlineStr">
+        <is>
+          <t>Tracey de Jager</t>
+        </is>
+      </c>
+      <c r="X327" s="2" t="inlineStr">
+        <is>
+          <t>Trade and Operations Manager</t>
+        </is>
+      </c>
+      <c r="Y327" s="2" t="inlineStr"/>
+      <c r="Z327" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA327" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA327"/>
+  <dimension ref="A1:AA329"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35679,6 +35679,208 @@
       </c>
       <c r="AA327" s="2" t="inlineStr"/>
     </row>
+    <row r="328">
+      <c r="A328" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B328" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C328" s="2" t="inlineStr">
+        <is>
+          <t>56825</t>
+        </is>
+      </c>
+      <c r="D328" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E328" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F328" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G328" s="2" t="inlineStr">
+        <is>
+          <t>11D Kloof Nek Road</t>
+        </is>
+      </c>
+      <c r="H328" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I328" s="2" t="inlineStr">
+        <is>
+          <t>https://publik.co.za</t>
+        </is>
+      </c>
+      <c r="J328" s="2" t="inlineStr"/>
+      <c r="K328" s="2" t="inlineStr"/>
+      <c r="L328" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M328" s="2" t="inlineStr"/>
+      <c r="N328" s="2" t="inlineStr">
+        <is>
+          <t>winebar@publik.co.za</t>
+        </is>
+      </c>
+      <c r="O328" s="2" t="inlineStr"/>
+      <c r="P328" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q328" s="2" t="inlineStr">
+        <is>
+          <t>201637149207</t>
+        </is>
+      </c>
+      <c r="R328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publik-wine/</t>
+        </is>
+      </c>
+      <c r="S328" s="2" t="inlineStr"/>
+      <c r="T328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/publikwine</t>
+        </is>
+      </c>
+      <c r="U328" s="2" t="inlineStr"/>
+      <c r="V328" s="2" t="inlineStr"/>
+      <c r="W328" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Bodenstein</t>
+        </is>
+      </c>
+      <c r="X328" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y328" s="2" t="inlineStr"/>
+      <c r="Z328" s="2" t="inlineStr"/>
+      <c r="AA328" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-bodenstein-a31842272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B329" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="inlineStr">
+        <is>
+          <t>56825</t>
+        </is>
+      </c>
+      <c r="D329" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E329" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F329" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G329" s="2" t="inlineStr">
+        <is>
+          <t>11D Kloof Nek Road</t>
+        </is>
+      </c>
+      <c r="H329" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I329" s="2" t="inlineStr">
+        <is>
+          <t>https://publik.co.za</t>
+        </is>
+      </c>
+      <c r="J329" s="2" t="inlineStr"/>
+      <c r="K329" s="2" t="inlineStr"/>
+      <c r="L329" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M329" s="2" t="inlineStr"/>
+      <c r="N329" s="2" t="inlineStr">
+        <is>
+          <t>winebar@publik.co.za</t>
+        </is>
+      </c>
+      <c r="O329" s="2" t="inlineStr"/>
+      <c r="P329" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q329" s="2" t="inlineStr">
+        <is>
+          <t>201637149207</t>
+        </is>
+      </c>
+      <c r="R329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publik-wine/</t>
+        </is>
+      </c>
+      <c r="S329" s="2" t="inlineStr"/>
+      <c r="T329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/publikwine</t>
+        </is>
+      </c>
+      <c r="U329" s="2" t="inlineStr"/>
+      <c r="V329" s="2" t="inlineStr"/>
+      <c r="W329" s="2" t="inlineStr">
+        <is>
+          <t>Alex Greenleaf</t>
+        </is>
+      </c>
+      <c r="X329" s="2" t="inlineStr">
+        <is>
+          <t>Regional Manager</t>
+        </is>
+      </c>
+      <c r="Y329" s="2" t="inlineStr"/>
+      <c r="Z329" s="2" t="inlineStr"/>
+      <c r="AA329" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-greenleaf-03072360/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA329"/>
+  <dimension ref="A1:AA335"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -35881,6 +35881,592 @@
         </is>
       </c>
     </row>
+    <row r="330">
+      <c r="A330" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">FNB Distributors </t>
+        </is>
+      </c>
+      <c r="B330" s="2" t="inlineStr"/>
+      <c r="C330" s="2" t="inlineStr">
+        <is>
+          <t>168757</t>
+        </is>
+      </c>
+      <c r="D330" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E330" s="2" t="inlineStr">
+        <is>
+          <t>Paarl</t>
+        </is>
+      </c>
+      <c r="F330" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape</t>
+        </is>
+      </c>
+      <c r="G330" s="2" t="inlineStr">
+        <is>
+          <t>Corner of Tabak and Louws Street</t>
+        </is>
+      </c>
+      <c r="H330" s="2" t="inlineStr">
+        <is>
+          <t>7646</t>
+        </is>
+      </c>
+      <c r="I330" s="2" t="inlineStr">
+        <is>
+          <t>https://fnbdistributors.com</t>
+        </is>
+      </c>
+      <c r="J330" s="2" t="inlineStr"/>
+      <c r="K330" s="2" t="inlineStr"/>
+      <c r="L330" s="2" t="inlineStr"/>
+      <c r="M330" s="2" t="inlineStr"/>
+      <c r="N330" s="2" t="inlineStr">
+        <is>
+          <t>jaco@fnbdistributors.com</t>
+        </is>
+      </c>
+      <c r="O330" s="2" t="inlineStr"/>
+      <c r="P330" s="2" t="inlineStr"/>
+      <c r="Q330" s="2" t="inlineStr"/>
+      <c r="R330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/fnb-distributors/</t>
+        </is>
+      </c>
+      <c r="S330" s="2" t="inlineStr"/>
+      <c r="T330" s="2" t="inlineStr"/>
+      <c r="U330" s="2" t="inlineStr"/>
+      <c r="V330" s="2" t="inlineStr"/>
+      <c r="W330" s="2" t="inlineStr">
+        <is>
+          <t>Jaco Fourie</t>
+        </is>
+      </c>
+      <c r="X330" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y330" s="2" t="inlineStr"/>
+      <c r="Z330" s="2" t="inlineStr"/>
+      <c r="AA330" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jaco-fourie/</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B331" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C331" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="D331" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E331" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F331" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G331" s="2" t="inlineStr">
+        <is>
+          <t>31 Francis Street</t>
+        </is>
+      </c>
+      <c r="H331" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I331" s="2" t="inlineStr">
+        <is>
+          <t>https://trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="J331" s="2" t="inlineStr"/>
+      <c r="K331" s="2" t="inlineStr"/>
+      <c r="L331" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M331" s="2" t="inlineStr"/>
+      <c r="N331" s="2" t="inlineStr">
+        <is>
+          <t>info@trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="O331" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 035 1629</t>
+        </is>
+      </c>
+      <c r="P331" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q331" s="2" t="inlineStr">
+        <is>
+          <t>201315554807</t>
+        </is>
+      </c>
+      <c r="R331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trumanandorange/</t>
+        </is>
+      </c>
+      <c r="S331" s="2" t="inlineStr"/>
+      <c r="T331" s="2" t="inlineStr"/>
+      <c r="U331" s="2" t="inlineStr"/>
+      <c r="V331" s="2" t="inlineStr"/>
+      <c r="W331" s="2" t="inlineStr">
+        <is>
+          <t>James Stapelberg</t>
+        </is>
+      </c>
+      <c r="X331" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y331" s="2" t="inlineStr"/>
+      <c r="Z331" s="2" t="inlineStr"/>
+      <c r="AA331" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-stapelberg-b6725775/</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C332" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="D332" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E332" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F332" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G332" s="2" t="inlineStr">
+        <is>
+          <t>31 Francis Street</t>
+        </is>
+      </c>
+      <c r="H332" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I332" s="2" t="inlineStr">
+        <is>
+          <t>https://trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="J332" s="2" t="inlineStr"/>
+      <c r="K332" s="2" t="inlineStr"/>
+      <c r="L332" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M332" s="2" t="inlineStr"/>
+      <c r="N332" s="2" t="inlineStr">
+        <is>
+          <t>info@trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="O332" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 035 1629</t>
+        </is>
+      </c>
+      <c r="P332" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q332" s="2" t="inlineStr">
+        <is>
+          <t>201315554807</t>
+        </is>
+      </c>
+      <c r="R332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trumanandorange/</t>
+        </is>
+      </c>
+      <c r="S332" s="2" t="inlineStr"/>
+      <c r="T332" s="2" t="inlineStr"/>
+      <c r="U332" s="2" t="inlineStr"/>
+      <c r="V332" s="2" t="inlineStr"/>
+      <c r="W332" s="2" t="inlineStr">
+        <is>
+          <t>Jared Higgitt</t>
+        </is>
+      </c>
+      <c r="X332" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y332" s="2" t="inlineStr"/>
+      <c r="Z332" s="2" t="inlineStr"/>
+      <c r="AA332" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jared-higgitt-515a18194/</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Wholesalers Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B333" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Wholesalers Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C333" s="2" t="inlineStr">
+        <is>
+          <t>47232</t>
+        </is>
+      </c>
+      <c r="D333" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E333" s="2" t="inlineStr">
+        <is>
+          <t>Brakpan</t>
+        </is>
+      </c>
+      <c r="F333" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, Ekurhuleni Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G333" s="2" t="inlineStr">
+        <is>
+          <t>60 Porter Street</t>
+        </is>
+      </c>
+      <c r="H333" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="I333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.imperialwholesalers.co.za</t>
+        </is>
+      </c>
+      <c r="J333" s="2" t="inlineStr"/>
+      <c r="K333" s="2" t="inlineStr"/>
+      <c r="L333" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M333" s="2" t="inlineStr"/>
+      <c r="N333" s="2" t="inlineStr">
+        <is>
+          <t>info@imperialwholesalers.co.za</t>
+        </is>
+      </c>
+      <c r="O333" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 740 6042</t>
+        </is>
+      </c>
+      <c r="P333" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q333" s="2" t="inlineStr">
+        <is>
+          <t>199202540623</t>
+        </is>
+      </c>
+      <c r="R333" s="2" t="inlineStr"/>
+      <c r="S333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Imperial-Liquor-Wholesalers-PTY-LTD-61561611255856/</t>
+        </is>
+      </c>
+      <c r="T333" s="2" t="inlineStr"/>
+      <c r="U333" s="2" t="inlineStr"/>
+      <c r="V333" s="2" t="inlineStr"/>
+      <c r="W333" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Costa</t>
+        </is>
+      </c>
+      <c r="X333" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y333" s="2" t="inlineStr"/>
+      <c r="Z333" s="2" t="inlineStr"/>
+      <c r="AA333" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jorge-costa-b1511481</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B334" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C334" s="2" t="inlineStr">
+        <is>
+          <t>56825</t>
+        </is>
+      </c>
+      <c r="D334" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E334" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F334" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G334" s="2" t="inlineStr">
+        <is>
+          <t>11D Kloof Nek Road</t>
+        </is>
+      </c>
+      <c r="H334" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I334" s="2" t="inlineStr">
+        <is>
+          <t>https://publik.co.za</t>
+        </is>
+      </c>
+      <c r="J334" s="2" t="inlineStr"/>
+      <c r="K334" s="2" t="inlineStr"/>
+      <c r="L334" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M334" s="2" t="inlineStr"/>
+      <c r="N334" s="2" t="inlineStr">
+        <is>
+          <t>winebar@publik.co.za</t>
+        </is>
+      </c>
+      <c r="O334" s="2" t="inlineStr"/>
+      <c r="P334" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q334" s="2" t="inlineStr">
+        <is>
+          <t>201637149207</t>
+        </is>
+      </c>
+      <c r="R334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publik-wine/</t>
+        </is>
+      </c>
+      <c r="S334" s="2" t="inlineStr"/>
+      <c r="T334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/publikwine</t>
+        </is>
+      </c>
+      <c r="U334" s="2" t="inlineStr"/>
+      <c r="V334" s="2" t="inlineStr"/>
+      <c r="W334" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Bodenstein</t>
+        </is>
+      </c>
+      <c r="X334" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y334" s="2" t="inlineStr"/>
+      <c r="Z334" s="2" t="inlineStr"/>
+      <c r="AA334" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-bodenstein-a31842272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B335" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C335" s="2" t="inlineStr">
+        <is>
+          <t>56825</t>
+        </is>
+      </c>
+      <c r="D335" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E335" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F335" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G335" s="2" t="inlineStr">
+        <is>
+          <t>11D Kloof Nek Road</t>
+        </is>
+      </c>
+      <c r="H335" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I335" s="2" t="inlineStr">
+        <is>
+          <t>https://publik.co.za</t>
+        </is>
+      </c>
+      <c r="J335" s="2" t="inlineStr"/>
+      <c r="K335" s="2" t="inlineStr"/>
+      <c r="L335" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M335" s="2" t="inlineStr"/>
+      <c r="N335" s="2" t="inlineStr">
+        <is>
+          <t>winebar@publik.co.za</t>
+        </is>
+      </c>
+      <c r="O335" s="2" t="inlineStr"/>
+      <c r="P335" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q335" s="2" t="inlineStr">
+        <is>
+          <t>201637149207</t>
+        </is>
+      </c>
+      <c r="R335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publik-wine/</t>
+        </is>
+      </c>
+      <c r="S335" s="2" t="inlineStr"/>
+      <c r="T335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/publikwine</t>
+        </is>
+      </c>
+      <c r="U335" s="2" t="inlineStr"/>
+      <c r="V335" s="2" t="inlineStr"/>
+      <c r="W335" s="2" t="inlineStr">
+        <is>
+          <t>Alex Greenleaf</t>
+        </is>
+      </c>
+      <c r="X335" s="2" t="inlineStr">
+        <is>
+          <t>Regional Manager</t>
+        </is>
+      </c>
+      <c r="Y335" s="2" t="inlineStr"/>
+      <c r="Z335" s="2" t="inlineStr"/>
+      <c r="AA335" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-greenleaf-03072360/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA335"/>
+  <dimension ref="A1:AA349"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -36467,6 +36467,1320 @@
         </is>
       </c>
     </row>
+    <row r="336">
+      <c r="A336" s="2" t="inlineStr">
+        <is>
+          <t>President Hyper</t>
+        </is>
+      </c>
+      <c r="B336" s="2" t="inlineStr"/>
+      <c r="C336" s="2" t="inlineStr">
+        <is>
+          <t>168834</t>
+        </is>
+      </c>
+      <c r="D336" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E336" s="2" t="inlineStr">
+        <is>
+          <t>Krugersdorp</t>
+        </is>
+      </c>
+      <c r="F336" s="2" t="inlineStr"/>
+      <c r="G336" s="2" t="inlineStr">
+        <is>
+          <t>Pretoria St</t>
+        </is>
+      </c>
+      <c r="H336" s="2" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="I336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.presidenthyper.co.za</t>
+        </is>
+      </c>
+      <c r="J336" s="2" t="inlineStr"/>
+      <c r="K336" s="2" t="inlineStr"/>
+      <c r="L336" s="2" t="inlineStr"/>
+      <c r="M336" s="2" t="inlineStr"/>
+      <c r="N336" s="2" t="inlineStr">
+        <is>
+          <t>info@presidenthyper.co.za</t>
+        </is>
+      </c>
+      <c r="O336" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 951 3200</t>
+        </is>
+      </c>
+      <c r="P336" s="2" t="inlineStr"/>
+      <c r="Q336" s="2" t="inlineStr"/>
+      <c r="R336" s="2" t="inlineStr"/>
+      <c r="S336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/presidenthyper/</t>
+        </is>
+      </c>
+      <c r="T336" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/presidenthyper/</t>
+        </is>
+      </c>
+      <c r="U336" s="2" t="inlineStr"/>
+      <c r="V336" s="2" t="inlineStr"/>
+      <c r="W336" s="2" t="inlineStr">
+        <is>
+          <t>Theresia Taute</t>
+        </is>
+      </c>
+      <c r="X336" s="2" t="inlineStr">
+        <is>
+          <t>Senior Buyer</t>
+        </is>
+      </c>
+      <c r="Y336" s="2" t="inlineStr"/>
+      <c r="Z336" s="2" t="inlineStr"/>
+      <c r="AA336" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/theresia-taute-16b9b65a</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" s="2" t="inlineStr">
+        <is>
+          <t>President Hyper</t>
+        </is>
+      </c>
+      <c r="B337" s="2" t="inlineStr"/>
+      <c r="C337" s="2" t="inlineStr">
+        <is>
+          <t>168834</t>
+        </is>
+      </c>
+      <c r="D337" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E337" s="2" t="inlineStr">
+        <is>
+          <t>Krugersdorp</t>
+        </is>
+      </c>
+      <c r="F337" s="2" t="inlineStr"/>
+      <c r="G337" s="2" t="inlineStr">
+        <is>
+          <t>Pretoria St</t>
+        </is>
+      </c>
+      <c r="H337" s="2" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="I337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.presidenthyper.co.za</t>
+        </is>
+      </c>
+      <c r="J337" s="2" t="inlineStr"/>
+      <c r="K337" s="2" t="inlineStr"/>
+      <c r="L337" s="2" t="inlineStr"/>
+      <c r="M337" s="2" t="inlineStr"/>
+      <c r="N337" s="2" t="inlineStr">
+        <is>
+          <t>info@presidenthyper.co.za</t>
+        </is>
+      </c>
+      <c r="O337" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 951 3200</t>
+        </is>
+      </c>
+      <c r="P337" s="2" t="inlineStr"/>
+      <c r="Q337" s="2" t="inlineStr"/>
+      <c r="R337" s="2" t="inlineStr"/>
+      <c r="S337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/presidenthyper/</t>
+        </is>
+      </c>
+      <c r="T337" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/presidenthyper/</t>
+        </is>
+      </c>
+      <c r="U337" s="2" t="inlineStr"/>
+      <c r="V337" s="2" t="inlineStr"/>
+      <c r="W337" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mphande </t>
+        </is>
+      </c>
+      <c r="X337" s="2" t="inlineStr">
+        <is>
+          <t>Buyer</t>
+        </is>
+      </c>
+      <c r="Y337" s="2" t="inlineStr"/>
+      <c r="Z337" s="2" t="inlineStr"/>
+      <c r="AA337" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/gordon-g-mphande-02663476</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" s="2" t="inlineStr">
+        <is>
+          <t>President Hyper</t>
+        </is>
+      </c>
+      <c r="B338" s="2" t="inlineStr"/>
+      <c r="C338" s="2" t="inlineStr">
+        <is>
+          <t>168834</t>
+        </is>
+      </c>
+      <c r="D338" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E338" s="2" t="inlineStr">
+        <is>
+          <t>Krugersdorp</t>
+        </is>
+      </c>
+      <c r="F338" s="2" t="inlineStr"/>
+      <c r="G338" s="2" t="inlineStr">
+        <is>
+          <t>Pretoria St</t>
+        </is>
+      </c>
+      <c r="H338" s="2" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="I338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.presidenthyper.co.za</t>
+        </is>
+      </c>
+      <c r="J338" s="2" t="inlineStr"/>
+      <c r="K338" s="2" t="inlineStr"/>
+      <c r="L338" s="2" t="inlineStr"/>
+      <c r="M338" s="2" t="inlineStr"/>
+      <c r="N338" s="2" t="inlineStr">
+        <is>
+          <t>info@presidenthyper.co.za</t>
+        </is>
+      </c>
+      <c r="O338" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 951 3200</t>
+        </is>
+      </c>
+      <c r="P338" s="2" t="inlineStr"/>
+      <c r="Q338" s="2" t="inlineStr"/>
+      <c r="R338" s="2" t="inlineStr"/>
+      <c r="S338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/presidenthyper/</t>
+        </is>
+      </c>
+      <c r="T338" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/presidenthyper/</t>
+        </is>
+      </c>
+      <c r="U338" s="2" t="inlineStr"/>
+      <c r="V338" s="2" t="inlineStr"/>
+      <c r="W338" s="2" t="inlineStr">
+        <is>
+          <t>Dewald Oosthuizen</t>
+        </is>
+      </c>
+      <c r="X338" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y338" s="2" t="inlineStr"/>
+      <c r="Z338" s="2" t="inlineStr"/>
+      <c r="AA338" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/dewald-oosthuizen-258644194</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" s="2" t="inlineStr">
+        <is>
+          <t>President Hyper</t>
+        </is>
+      </c>
+      <c r="B339" s="2" t="inlineStr"/>
+      <c r="C339" s="2" t="inlineStr">
+        <is>
+          <t>168834</t>
+        </is>
+      </c>
+      <c r="D339" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E339" s="2" t="inlineStr">
+        <is>
+          <t>Krugersdorp</t>
+        </is>
+      </c>
+      <c r="F339" s="2" t="inlineStr"/>
+      <c r="G339" s="2" t="inlineStr">
+        <is>
+          <t>Pretoria St</t>
+        </is>
+      </c>
+      <c r="H339" s="2" t="inlineStr">
+        <is>
+          <t>1739</t>
+        </is>
+      </c>
+      <c r="I339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.presidenthyper.co.za</t>
+        </is>
+      </c>
+      <c r="J339" s="2" t="inlineStr"/>
+      <c r="K339" s="2" t="inlineStr"/>
+      <c r="L339" s="2" t="inlineStr"/>
+      <c r="M339" s="2" t="inlineStr"/>
+      <c r="N339" s="2" t="inlineStr">
+        <is>
+          <t>info@presidenthyper.co.za</t>
+        </is>
+      </c>
+      <c r="O339" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 951 3200</t>
+        </is>
+      </c>
+      <c r="P339" s="2" t="inlineStr"/>
+      <c r="Q339" s="2" t="inlineStr"/>
+      <c r="R339" s="2" t="inlineStr"/>
+      <c r="S339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/presidenthyper/</t>
+        </is>
+      </c>
+      <c r="T339" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/presidenthyper/</t>
+        </is>
+      </c>
+      <c r="U339" s="2" t="inlineStr"/>
+      <c r="V339" s="2" t="inlineStr"/>
+      <c r="W339" s="2" t="inlineStr">
+        <is>
+          <t>Elsa Vaal</t>
+        </is>
+      </c>
+      <c r="X339" s="2" t="inlineStr">
+        <is>
+          <t>Senior Buyer</t>
+        </is>
+      </c>
+      <c r="Y339" s="2" t="inlineStr"/>
+      <c r="Z339" s="2" t="inlineStr"/>
+      <c r="AA339" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/elsa-vaal-924a63123</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" s="2" t="inlineStr">
+        <is>
+          <t>Ultra Liquors - Cresta</t>
+        </is>
+      </c>
+      <c r="B340" s="2" t="inlineStr"/>
+      <c r="C340" s="2" t="inlineStr">
+        <is>
+          <t>168833</t>
+        </is>
+      </c>
+      <c r="D340" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E340" s="2" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="F340" s="2" t="inlineStr"/>
+      <c r="G340" s="2" t="inlineStr">
+        <is>
+          <t>67 Roscommon Road, Cnr Dundalk Road, Parkview</t>
+        </is>
+      </c>
+      <c r="H340" s="2" t="inlineStr"/>
+      <c r="I340" s="2" t="inlineStr">
+        <is>
+          <t>https://cresta.ultraliquors.co.za</t>
+        </is>
+      </c>
+      <c r="J340" s="2" t="inlineStr"/>
+      <c r="K340" s="2" t="inlineStr"/>
+      <c r="L340" s="2" t="inlineStr"/>
+      <c r="M340" s="2" t="inlineStr"/>
+      <c r="N340" s="2" t="inlineStr">
+        <is>
+          <t>headoffice@ultraliquors.co.za</t>
+        </is>
+      </c>
+      <c r="O340" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 565 8563</t>
+        </is>
+      </c>
+      <c r="P340" s="2" t="inlineStr"/>
+      <c r="Q340" s="2" t="inlineStr"/>
+      <c r="R340" s="2" t="inlineStr"/>
+      <c r="S340" s="2" t="inlineStr"/>
+      <c r="T340" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ultraliquors/</t>
+        </is>
+      </c>
+      <c r="U340" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ultraliquors</t>
+        </is>
+      </c>
+      <c r="V340" s="2" t="inlineStr"/>
+      <c r="W340" s="2" t="inlineStr">
+        <is>
+          <t>Jolene Witt</t>
+        </is>
+      </c>
+      <c r="X340" s="2" t="inlineStr">
+        <is>
+          <t>Category Management Manager</t>
+        </is>
+      </c>
+      <c r="Y340" s="2" t="inlineStr"/>
+      <c r="Z340" s="2" t="inlineStr"/>
+      <c r="AA340" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/jolene-de-witt-817861359</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" s="2" t="inlineStr">
+        <is>
+          <t>Ultra Liquors - Cresta</t>
+        </is>
+      </c>
+      <c r="B341" s="2" t="inlineStr"/>
+      <c r="C341" s="2" t="inlineStr">
+        <is>
+          <t>168833</t>
+        </is>
+      </c>
+      <c r="D341" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E341" s="2" t="inlineStr">
+        <is>
+          <t>Johannesburg</t>
+        </is>
+      </c>
+      <c r="F341" s="2" t="inlineStr"/>
+      <c r="G341" s="2" t="inlineStr">
+        <is>
+          <t>67 Roscommon Road, Cnr Dundalk Road, Parkview</t>
+        </is>
+      </c>
+      <c r="H341" s="2" t="inlineStr"/>
+      <c r="I341" s="2" t="inlineStr">
+        <is>
+          <t>https://cresta.ultraliquors.co.za</t>
+        </is>
+      </c>
+      <c r="J341" s="2" t="inlineStr"/>
+      <c r="K341" s="2" t="inlineStr"/>
+      <c r="L341" s="2" t="inlineStr"/>
+      <c r="M341" s="2" t="inlineStr"/>
+      <c r="N341" s="2" t="inlineStr">
+        <is>
+          <t>headoffice@ultraliquors.co.za</t>
+        </is>
+      </c>
+      <c r="O341" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 565 8563</t>
+        </is>
+      </c>
+      <c r="P341" s="2" t="inlineStr"/>
+      <c r="Q341" s="2" t="inlineStr"/>
+      <c r="R341" s="2" t="inlineStr"/>
+      <c r="S341" s="2" t="inlineStr"/>
+      <c r="T341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/ultraliquors/</t>
+        </is>
+      </c>
+      <c r="U341" s="2" t="inlineStr">
+        <is>
+          <t>https://twitter.com/ultraliquors</t>
+        </is>
+      </c>
+      <c r="V341" s="2" t="inlineStr"/>
+      <c r="W341" s="2" t="inlineStr">
+        <is>
+          <t>Tony Conde</t>
+        </is>
+      </c>
+      <c r="X341" s="2" t="inlineStr">
+        <is>
+          <t>National Category Manager Spirits, Beer &amp; Ciders</t>
+        </is>
+      </c>
+      <c r="Y341" s="2" t="inlineStr"/>
+      <c r="Z341" s="2" t="inlineStr"/>
+      <c r="AA341" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/tony-conde-05339868/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" s="2" t="inlineStr">
+        <is>
+          <t>Vinimark Trading (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B342" s="2" t="inlineStr">
+        <is>
+          <t>Vinimark Trading (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C342" s="2" t="inlineStr">
+        <is>
+          <t>11972</t>
+        </is>
+      </c>
+      <c r="D342" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E342" s="2" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="F342" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Cape Winelands</t>
+        </is>
+      </c>
+      <c r="G342" s="2" t="inlineStr">
+        <is>
+          <t>5 Herold Street</t>
+        </is>
+      </c>
+      <c r="H342" s="2" t="inlineStr">
+        <is>
+          <t>7600</t>
+        </is>
+      </c>
+      <c r="I342" s="2" t="inlineStr">
+        <is>
+          <t>https://vinimark.co.za</t>
+        </is>
+      </c>
+      <c r="J342" s="2" t="inlineStr"/>
+      <c r="K342" s="2" t="inlineStr"/>
+      <c r="L342" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M342" s="2" t="inlineStr"/>
+      <c r="N342" s="2" t="inlineStr">
+        <is>
+          <t>info@vinimark.co.za</t>
+        </is>
+      </c>
+      <c r="O342" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 883 8043</t>
+        </is>
+      </c>
+      <c r="P342" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q342" s="2" t="inlineStr">
+        <is>
+          <t>198700003207</t>
+        </is>
+      </c>
+      <c r="R342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinimark-the-wine-company/</t>
+        </is>
+      </c>
+      <c r="S342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinimarkWine</t>
+        </is>
+      </c>
+      <c r="T342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinimarkwine</t>
+        </is>
+      </c>
+      <c r="U342" s="2" t="inlineStr"/>
+      <c r="V342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCMdaEV70F819_0jpZKII0hg</t>
+        </is>
+      </c>
+      <c r="W342" s="2" t="inlineStr">
+        <is>
+          <t>Eugene Sylvester</t>
+        </is>
+      </c>
+      <c r="X342" s="2" t="inlineStr">
+        <is>
+          <t>Sales Consultant</t>
+        </is>
+      </c>
+      <c r="Y342" s="2" t="inlineStr"/>
+      <c r="Z342" s="2" t="inlineStr"/>
+      <c r="AA342" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eugene-sylvester-72800797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Vinimark Trading (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Vinimark Trading (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C343" s="2" t="inlineStr">
+        <is>
+          <t>11972</t>
+        </is>
+      </c>
+      <c r="D343" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E343" s="2" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="F343" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Cape Winelands</t>
+        </is>
+      </c>
+      <c r="G343" s="2" t="inlineStr">
+        <is>
+          <t>5 Herold Street</t>
+        </is>
+      </c>
+      <c r="H343" s="2" t="inlineStr">
+        <is>
+          <t>7600</t>
+        </is>
+      </c>
+      <c r="I343" s="2" t="inlineStr">
+        <is>
+          <t>https://vinimark.co.za</t>
+        </is>
+      </c>
+      <c r="J343" s="2" t="inlineStr"/>
+      <c r="K343" s="2" t="inlineStr"/>
+      <c r="L343" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M343" s="2" t="inlineStr"/>
+      <c r="N343" s="2" t="inlineStr">
+        <is>
+          <t>info@vinimark.co.za</t>
+        </is>
+      </c>
+      <c r="O343" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 883 8043</t>
+        </is>
+      </c>
+      <c r="P343" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q343" s="2" t="inlineStr">
+        <is>
+          <t>198700003207</t>
+        </is>
+      </c>
+      <c r="R343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinimark-the-wine-company/</t>
+        </is>
+      </c>
+      <c r="S343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinimarkWine</t>
+        </is>
+      </c>
+      <c r="T343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinimarkwine</t>
+        </is>
+      </c>
+      <c r="U343" s="2" t="inlineStr"/>
+      <c r="V343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCMdaEV70F819_0jpZKII0hg</t>
+        </is>
+      </c>
+      <c r="W343" s="2" t="inlineStr">
+        <is>
+          <t>Eckhardt Gerber</t>
+        </is>
+      </c>
+      <c r="X343" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y343" s="2" t="inlineStr"/>
+      <c r="Z343" s="2" t="inlineStr"/>
+      <c r="AA343" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eckhardt-gerber-b93ba76</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" s="2" t="inlineStr">
+        <is>
+          <t>Jjb Liquor Masters Cc</t>
+        </is>
+      </c>
+      <c r="B344" s="2" t="inlineStr">
+        <is>
+          <t>Jjb Liquor Masters Cc</t>
+        </is>
+      </c>
+      <c r="C344" s="2" t="inlineStr">
+        <is>
+          <t>115577</t>
+        </is>
+      </c>
+      <c r="D344" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E344" s="2" t="inlineStr">
+        <is>
+          <t>Roodepoort</t>
+        </is>
+      </c>
+      <c r="F344" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G344" s="2" t="inlineStr">
+        <is>
+          <t>145 Main Road</t>
+        </is>
+      </c>
+      <c r="H344" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="I344" s="2" t="inlineStr"/>
+      <c r="J344" s="2" t="inlineStr"/>
+      <c r="K344" s="2" t="inlineStr"/>
+      <c r="L344" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M344" s="2" t="inlineStr"/>
+      <c r="N344" s="2" t="inlineStr">
+        <is>
+          <t>jakesliquormasters@gmail.com</t>
+        </is>
+      </c>
+      <c r="O344" s="2" t="inlineStr"/>
+      <c r="P344" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q344" s="2" t="inlineStr">
+        <is>
+          <t>200915989023</t>
+        </is>
+      </c>
+      <c r="R344" s="2" t="inlineStr"/>
+      <c r="S344" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pg/jakesliquormasters</t>
+        </is>
+      </c>
+      <c r="T344" s="2" t="inlineStr"/>
+      <c r="U344" s="2" t="inlineStr"/>
+      <c r="V344" s="2" t="inlineStr"/>
+      <c r="W344" s="2" t="inlineStr"/>
+      <c r="X344" s="2" t="inlineStr"/>
+      <c r="Y344" s="2" t="inlineStr"/>
+      <c r="Z344" s="2" t="inlineStr"/>
+      <c r="AA344" s="2" t="inlineStr"/>
+    </row>
+    <row r="345">
+      <c r="A345" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B345" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C345" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="D345" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E345" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F345" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G345" s="2" t="inlineStr">
+        <is>
+          <t>31 Francis Street</t>
+        </is>
+      </c>
+      <c r="H345" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I345" s="2" t="inlineStr">
+        <is>
+          <t>https://trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="J345" s="2" t="inlineStr"/>
+      <c r="K345" s="2" t="inlineStr"/>
+      <c r="L345" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M345" s="2" t="inlineStr"/>
+      <c r="N345" s="2" t="inlineStr">
+        <is>
+          <t>info@trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="O345" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 035 1629</t>
+        </is>
+      </c>
+      <c r="P345" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q345" s="2" t="inlineStr">
+        <is>
+          <t>201315554807</t>
+        </is>
+      </c>
+      <c r="R345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trumanandorange/</t>
+        </is>
+      </c>
+      <c r="S345" s="2" t="inlineStr"/>
+      <c r="T345" s="2" t="inlineStr"/>
+      <c r="U345" s="2" t="inlineStr"/>
+      <c r="V345" s="2" t="inlineStr"/>
+      <c r="W345" s="2" t="inlineStr">
+        <is>
+          <t>James Stapelberg</t>
+        </is>
+      </c>
+      <c r="X345" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y345" s="2" t="inlineStr"/>
+      <c r="Z345" s="2" t="inlineStr"/>
+      <c r="AA345" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-stapelberg-b6725775/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B346" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C346" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="D346" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E346" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F346" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G346" s="2" t="inlineStr">
+        <is>
+          <t>31 Francis Street</t>
+        </is>
+      </c>
+      <c r="H346" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I346" s="2" t="inlineStr">
+        <is>
+          <t>https://trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="J346" s="2" t="inlineStr"/>
+      <c r="K346" s="2" t="inlineStr"/>
+      <c r="L346" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M346" s="2" t="inlineStr"/>
+      <c r="N346" s="2" t="inlineStr">
+        <is>
+          <t>info@trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="O346" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 035 1629</t>
+        </is>
+      </c>
+      <c r="P346" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q346" s="2" t="inlineStr">
+        <is>
+          <t>201315554807</t>
+        </is>
+      </c>
+      <c r="R346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trumanandorange/</t>
+        </is>
+      </c>
+      <c r="S346" s="2" t="inlineStr"/>
+      <c r="T346" s="2" t="inlineStr"/>
+      <c r="U346" s="2" t="inlineStr"/>
+      <c r="V346" s="2" t="inlineStr"/>
+      <c r="W346" s="2" t="inlineStr">
+        <is>
+          <t>Jared Higgitt</t>
+        </is>
+      </c>
+      <c r="X346" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y346" s="2" t="inlineStr"/>
+      <c r="Z346" s="2" t="inlineStr"/>
+      <c r="AA346" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jared-higgitt-515a18194/</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Wholesalers Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B347" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Wholesalers Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C347" s="2" t="inlineStr">
+        <is>
+          <t>47232</t>
+        </is>
+      </c>
+      <c r="D347" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E347" s="2" t="inlineStr">
+        <is>
+          <t>Brakpan</t>
+        </is>
+      </c>
+      <c r="F347" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, Ekurhuleni Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G347" s="2" t="inlineStr">
+        <is>
+          <t>60 Porter Street</t>
+        </is>
+      </c>
+      <c r="H347" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="I347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.imperialwholesalers.co.za</t>
+        </is>
+      </c>
+      <c r="J347" s="2" t="inlineStr"/>
+      <c r="K347" s="2" t="inlineStr"/>
+      <c r="L347" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M347" s="2" t="inlineStr"/>
+      <c r="N347" s="2" t="inlineStr">
+        <is>
+          <t>info@imperialwholesalers.co.za</t>
+        </is>
+      </c>
+      <c r="O347" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 740 6042</t>
+        </is>
+      </c>
+      <c r="P347" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q347" s="2" t="inlineStr">
+        <is>
+          <t>199202540623</t>
+        </is>
+      </c>
+      <c r="R347" s="2" t="inlineStr"/>
+      <c r="S347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Imperial-Liquor-Wholesalers-PTY-LTD-61561611255856/</t>
+        </is>
+      </c>
+      <c r="T347" s="2" t="inlineStr"/>
+      <c r="U347" s="2" t="inlineStr"/>
+      <c r="V347" s="2" t="inlineStr"/>
+      <c r="W347" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Costa</t>
+        </is>
+      </c>
+      <c r="X347" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y347" s="2" t="inlineStr"/>
+      <c r="Z347" s="2" t="inlineStr"/>
+      <c r="AA347" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jorge-costa-b1511481</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B348" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C348" s="2" t="inlineStr">
+        <is>
+          <t>56825</t>
+        </is>
+      </c>
+      <c r="D348" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E348" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F348" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G348" s="2" t="inlineStr">
+        <is>
+          <t>11D Kloof Nek Road</t>
+        </is>
+      </c>
+      <c r="H348" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I348" s="2" t="inlineStr">
+        <is>
+          <t>https://publik.co.za</t>
+        </is>
+      </c>
+      <c r="J348" s="2" t="inlineStr"/>
+      <c r="K348" s="2" t="inlineStr"/>
+      <c r="L348" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M348" s="2" t="inlineStr"/>
+      <c r="N348" s="2" t="inlineStr">
+        <is>
+          <t>winebar@publik.co.za</t>
+        </is>
+      </c>
+      <c r="O348" s="2" t="inlineStr"/>
+      <c r="P348" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q348" s="2" t="inlineStr">
+        <is>
+          <t>201637149207</t>
+        </is>
+      </c>
+      <c r="R348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publik-wine/</t>
+        </is>
+      </c>
+      <c r="S348" s="2" t="inlineStr"/>
+      <c r="T348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/publikwine</t>
+        </is>
+      </c>
+      <c r="U348" s="2" t="inlineStr"/>
+      <c r="V348" s="2" t="inlineStr"/>
+      <c r="W348" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Bodenstein</t>
+        </is>
+      </c>
+      <c r="X348" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y348" s="2" t="inlineStr"/>
+      <c r="Z348" s="2" t="inlineStr"/>
+      <c r="AA348" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-bodenstein-a31842272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B349" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C349" s="2" t="inlineStr">
+        <is>
+          <t>56825</t>
+        </is>
+      </c>
+      <c r="D349" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E349" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F349" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G349" s="2" t="inlineStr">
+        <is>
+          <t>11D Kloof Nek Road</t>
+        </is>
+      </c>
+      <c r="H349" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I349" s="2" t="inlineStr">
+        <is>
+          <t>https://publik.co.za</t>
+        </is>
+      </c>
+      <c r="J349" s="2" t="inlineStr"/>
+      <c r="K349" s="2" t="inlineStr"/>
+      <c r="L349" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M349" s="2" t="inlineStr"/>
+      <c r="N349" s="2" t="inlineStr">
+        <is>
+          <t>winebar@publik.co.za</t>
+        </is>
+      </c>
+      <c r="O349" s="2" t="inlineStr"/>
+      <c r="P349" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q349" s="2" t="inlineStr">
+        <is>
+          <t>201637149207</t>
+        </is>
+      </c>
+      <c r="R349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publik-wine/</t>
+        </is>
+      </c>
+      <c r="S349" s="2" t="inlineStr"/>
+      <c r="T349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/publikwine</t>
+        </is>
+      </c>
+      <c r="U349" s="2" t="inlineStr"/>
+      <c r="V349" s="2" t="inlineStr"/>
+      <c r="W349" s="2" t="inlineStr">
+        <is>
+          <t>Alex Greenleaf</t>
+        </is>
+      </c>
+      <c r="X349" s="2" t="inlineStr">
+        <is>
+          <t>Regional Manager</t>
+        </is>
+      </c>
+      <c r="Y349" s="2" t="inlineStr"/>
+      <c r="Z349" s="2" t="inlineStr"/>
+      <c r="AA349" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-greenleaf-03072360/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/BWI/bestwine_output/bestwine_South Africa.xlsx
+++ b/BWI/bestwine_output/bestwine_South Africa.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA349"/>
+  <dimension ref="A1:AA359"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -37781,6 +37781,992 @@
         </is>
       </c>
     </row>
+    <row r="350">
+      <c r="A350" s="2" t="inlineStr">
+        <is>
+          <t>Wine On Time Distribution Cc</t>
+        </is>
+      </c>
+      <c r="B350" s="2" t="inlineStr">
+        <is>
+          <t>Wine On Time Distribution Cc</t>
+        </is>
+      </c>
+      <c r="C350" s="2" t="inlineStr">
+        <is>
+          <t>122708</t>
+        </is>
+      </c>
+      <c r="D350" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E350" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F350" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G350" s="2" t="inlineStr">
+        <is>
+          <t>113 Cannon Island Way</t>
+        </is>
+      </c>
+      <c r="H350" s="2" t="inlineStr">
+        <is>
+          <t>7945</t>
+        </is>
+      </c>
+      <c r="I350" s="2" t="inlineStr">
+        <is>
+          <t>https://wineontime.co.za</t>
+        </is>
+      </c>
+      <c r="J350" s="2" t="inlineStr"/>
+      <c r="K350" s="2" t="inlineStr"/>
+      <c r="L350" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="M350" s="2" t="inlineStr"/>
+      <c r="N350" s="2" t="inlineStr">
+        <is>
+          <t>orders@wineontime.co.za</t>
+        </is>
+      </c>
+      <c r="O350" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 788 1179</t>
+        </is>
+      </c>
+      <c r="P350" s="2" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="Q350" s="2" t="inlineStr">
+        <is>
+          <t>200808080923</t>
+        </is>
+      </c>
+      <c r="R350" s="2" t="inlineStr"/>
+      <c r="S350" s="2" t="inlineStr"/>
+      <c r="T350" s="2" t="inlineStr"/>
+      <c r="U350" s="2" t="inlineStr"/>
+      <c r="V350" s="2" t="inlineStr"/>
+      <c r="W350" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Debbie </t>
+        </is>
+      </c>
+      <c r="X350" s="2" t="inlineStr">
+        <is>
+          <t>Manager</t>
+        </is>
+      </c>
+      <c r="Y350" s="2" t="inlineStr"/>
+      <c r="Z350" s="2" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="AA350" s="2" t="inlineStr"/>
+    </row>
+    <row r="351">
+      <c r="A351" s="2" t="inlineStr">
+        <is>
+          <t>Cellarclub</t>
+        </is>
+      </c>
+      <c r="B351" s="2" t="inlineStr">
+        <is>
+          <t>Cellarclub</t>
+        </is>
+      </c>
+      <c r="C351" s="2" t="inlineStr">
+        <is>
+          <t>122640</t>
+        </is>
+      </c>
+      <c r="D351" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E351" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F351" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G351" s="2" t="inlineStr">
+        <is>
+          <t>Clock Tower Retail Centre,  Portswood Road</t>
+        </is>
+      </c>
+      <c r="H351" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I351" s="2" t="inlineStr">
+        <is>
+          <t>https://cellarclub.co.za</t>
+        </is>
+      </c>
+      <c r="J351" s="2" t="inlineStr"/>
+      <c r="K351" s="2" t="inlineStr"/>
+      <c r="L351" s="2" t="inlineStr"/>
+      <c r="M351" s="2" t="inlineStr"/>
+      <c r="N351" s="2" t="inlineStr">
+        <is>
+          <t>info@cellarclub.co.za</t>
+        </is>
+      </c>
+      <c r="O351" s="2" t="inlineStr"/>
+      <c r="P351" s="2" t="inlineStr"/>
+      <c r="Q351" s="2" t="inlineStr"/>
+      <c r="R351" s="2" t="inlineStr"/>
+      <c r="S351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/CellarClubTunnel/</t>
+        </is>
+      </c>
+      <c r="T351" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/cellarclubstore/</t>
+        </is>
+      </c>
+      <c r="U351" s="2" t="inlineStr"/>
+      <c r="V351" s="2" t="inlineStr"/>
+      <c r="W351" s="2" t="inlineStr"/>
+      <c r="X351" s="2" t="inlineStr"/>
+      <c r="Y351" s="2" t="inlineStr"/>
+      <c r="Z351" s="2" t="inlineStr"/>
+      <c r="AA351" s="2" t="inlineStr"/>
+    </row>
+    <row r="352">
+      <c r="A352" s="2" t="inlineStr">
+        <is>
+          <t>Vinimark Trading (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B352" s="2" t="inlineStr">
+        <is>
+          <t>Vinimark Trading (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C352" s="2" t="inlineStr">
+        <is>
+          <t>11972</t>
+        </is>
+      </c>
+      <c r="D352" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E352" s="2" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="F352" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Cape Winelands</t>
+        </is>
+      </c>
+      <c r="G352" s="2" t="inlineStr">
+        <is>
+          <t>5 Herold Street</t>
+        </is>
+      </c>
+      <c r="H352" s="2" t="inlineStr">
+        <is>
+          <t>7600</t>
+        </is>
+      </c>
+      <c r="I352" s="2" t="inlineStr">
+        <is>
+          <t>https://vinimark.co.za</t>
+        </is>
+      </c>
+      <c r="J352" s="2" t="inlineStr"/>
+      <c r="K352" s="2" t="inlineStr"/>
+      <c r="L352" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M352" s="2" t="inlineStr"/>
+      <c r="N352" s="2" t="inlineStr">
+        <is>
+          <t>info@vinimark.co.za</t>
+        </is>
+      </c>
+      <c r="O352" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 883 8043</t>
+        </is>
+      </c>
+      <c r="P352" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q352" s="2" t="inlineStr">
+        <is>
+          <t>198700003207</t>
+        </is>
+      </c>
+      <c r="R352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinimark-the-wine-company/</t>
+        </is>
+      </c>
+      <c r="S352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinimarkWine</t>
+        </is>
+      </c>
+      <c r="T352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinimarkwine</t>
+        </is>
+      </c>
+      <c r="U352" s="2" t="inlineStr"/>
+      <c r="V352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCMdaEV70F819_0jpZKII0hg</t>
+        </is>
+      </c>
+      <c r="W352" s="2" t="inlineStr">
+        <is>
+          <t>Eugene Sylvester</t>
+        </is>
+      </c>
+      <c r="X352" s="2" t="inlineStr">
+        <is>
+          <t>Sales Consultant</t>
+        </is>
+      </c>
+      <c r="Y352" s="2" t="inlineStr"/>
+      <c r="Z352" s="2" t="inlineStr"/>
+      <c r="AA352" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eugene-sylvester-72800797/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" s="2" t="inlineStr">
+        <is>
+          <t>Vinimark Trading (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B353" s="2" t="inlineStr">
+        <is>
+          <t>Vinimark Trading (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C353" s="2" t="inlineStr">
+        <is>
+          <t>11972</t>
+        </is>
+      </c>
+      <c r="D353" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E353" s="2" t="inlineStr">
+        <is>
+          <t>Stellenbosch</t>
+        </is>
+      </c>
+      <c r="F353" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, Cape Winelands</t>
+        </is>
+      </c>
+      <c r="G353" s="2" t="inlineStr">
+        <is>
+          <t>5 Herold Street</t>
+        </is>
+      </c>
+      <c r="H353" s="2" t="inlineStr">
+        <is>
+          <t>7600</t>
+        </is>
+      </c>
+      <c r="I353" s="2" t="inlineStr">
+        <is>
+          <t>https://vinimark.co.za</t>
+        </is>
+      </c>
+      <c r="J353" s="2" t="inlineStr"/>
+      <c r="K353" s="2" t="inlineStr"/>
+      <c r="L353" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="M353" s="2" t="inlineStr"/>
+      <c r="N353" s="2" t="inlineStr">
+        <is>
+          <t>info@vinimark.co.za</t>
+        </is>
+      </c>
+      <c r="O353" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 883 8043</t>
+        </is>
+      </c>
+      <c r="P353" s="2" t="inlineStr">
+        <is>
+          <t>1987</t>
+        </is>
+      </c>
+      <c r="Q353" s="2" t="inlineStr">
+        <is>
+          <t>198700003207</t>
+        </is>
+      </c>
+      <c r="R353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/vinimark-the-wine-company/</t>
+        </is>
+      </c>
+      <c r="S353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/VinimarkWine</t>
+        </is>
+      </c>
+      <c r="T353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/vinimarkwine</t>
+        </is>
+      </c>
+      <c r="U353" s="2" t="inlineStr"/>
+      <c r="V353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/channel/UCMdaEV70F819_0jpZKII0hg</t>
+        </is>
+      </c>
+      <c r="W353" s="2" t="inlineStr">
+        <is>
+          <t>Eckhardt Gerber</t>
+        </is>
+      </c>
+      <c r="X353" s="2" t="inlineStr">
+        <is>
+          <t>Ceo</t>
+        </is>
+      </c>
+      <c r="Y353" s="2" t="inlineStr"/>
+      <c r="Z353" s="2" t="inlineStr"/>
+      <c r="AA353" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/eckhardt-gerber-b93ba76</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>Jjb Liquor Masters Cc</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Jjb Liquor Masters Cc</t>
+        </is>
+      </c>
+      <c r="C354" s="2" t="inlineStr">
+        <is>
+          <t>115577</t>
+        </is>
+      </c>
+      <c r="D354" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E354" s="2" t="inlineStr">
+        <is>
+          <t>Roodepoort</t>
+        </is>
+      </c>
+      <c r="F354" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, City of Johannesburg Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G354" s="2" t="inlineStr">
+        <is>
+          <t>145 Main Road</t>
+        </is>
+      </c>
+      <c r="H354" s="2" t="inlineStr">
+        <is>
+          <t>1708</t>
+        </is>
+      </c>
+      <c r="I354" s="2" t="inlineStr"/>
+      <c r="J354" s="2" t="inlineStr"/>
+      <c r="K354" s="2" t="inlineStr"/>
+      <c r="L354" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="M354" s="2" t="inlineStr"/>
+      <c r="N354" s="2" t="inlineStr">
+        <is>
+          <t>jakesliquormasters@gmail.com</t>
+        </is>
+      </c>
+      <c r="O354" s="2" t="inlineStr"/>
+      <c r="P354" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="Q354" s="2" t="inlineStr">
+        <is>
+          <t>200915989023</t>
+        </is>
+      </c>
+      <c r="R354" s="2" t="inlineStr"/>
+      <c r="S354" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/pg/jakesliquormasters</t>
+        </is>
+      </c>
+      <c r="T354" s="2" t="inlineStr"/>
+      <c r="U354" s="2" t="inlineStr"/>
+      <c r="V354" s="2" t="inlineStr"/>
+      <c r="W354" s="2" t="inlineStr"/>
+      <c r="X354" s="2" t="inlineStr"/>
+      <c r="Y354" s="2" t="inlineStr"/>
+      <c r="Z354" s="2" t="inlineStr"/>
+      <c r="AA354" s="2" t="inlineStr"/>
+    </row>
+    <row r="355">
+      <c r="A355" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B355" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C355" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="D355" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E355" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F355" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G355" s="2" t="inlineStr">
+        <is>
+          <t>31 Francis Street</t>
+        </is>
+      </c>
+      <c r="H355" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I355" s="2" t="inlineStr">
+        <is>
+          <t>https://trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="J355" s="2" t="inlineStr"/>
+      <c r="K355" s="2" t="inlineStr"/>
+      <c r="L355" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M355" s="2" t="inlineStr"/>
+      <c r="N355" s="2" t="inlineStr">
+        <is>
+          <t>info@trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="O355" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 035 1629</t>
+        </is>
+      </c>
+      <c r="P355" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q355" s="2" t="inlineStr">
+        <is>
+          <t>201315554807</t>
+        </is>
+      </c>
+      <c r="R355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trumanandorange/</t>
+        </is>
+      </c>
+      <c r="S355" s="2" t="inlineStr"/>
+      <c r="T355" s="2" t="inlineStr"/>
+      <c r="U355" s="2" t="inlineStr"/>
+      <c r="V355" s="2" t="inlineStr"/>
+      <c r="W355" s="2" t="inlineStr">
+        <is>
+          <t>James Stapelberg</t>
+        </is>
+      </c>
+      <c r="X355" s="2" t="inlineStr">
+        <is>
+          <t>Brand Manager</t>
+        </is>
+      </c>
+      <c r="Y355" s="2" t="inlineStr"/>
+      <c r="Z355" s="2" t="inlineStr"/>
+      <c r="AA355" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/james-stapelberg-b6725775/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B356" s="2" t="inlineStr">
+        <is>
+          <t>Truman And Orange (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C356" s="2" t="inlineStr">
+        <is>
+          <t>47036</t>
+        </is>
+      </c>
+      <c r="D356" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E356" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F356" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G356" s="2" t="inlineStr">
+        <is>
+          <t>31 Francis Street</t>
+        </is>
+      </c>
+      <c r="H356" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I356" s="2" t="inlineStr">
+        <is>
+          <t>https://trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="J356" s="2" t="inlineStr"/>
+      <c r="K356" s="2" t="inlineStr"/>
+      <c r="L356" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="M356" s="2" t="inlineStr"/>
+      <c r="N356" s="2" t="inlineStr">
+        <is>
+          <t>info@trumanandorange.com</t>
+        </is>
+      </c>
+      <c r="O356" s="2" t="inlineStr">
+        <is>
+          <t>+27 21 035 1629</t>
+        </is>
+      </c>
+      <c r="P356" s="2" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="Q356" s="2" t="inlineStr">
+        <is>
+          <t>201315554807</t>
+        </is>
+      </c>
+      <c r="R356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/trumanandorange/</t>
+        </is>
+      </c>
+      <c r="S356" s="2" t="inlineStr"/>
+      <c r="T356" s="2" t="inlineStr"/>
+      <c r="U356" s="2" t="inlineStr"/>
+      <c r="V356" s="2" t="inlineStr"/>
+      <c r="W356" s="2" t="inlineStr">
+        <is>
+          <t>Jared Higgitt</t>
+        </is>
+      </c>
+      <c r="X356" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y356" s="2" t="inlineStr"/>
+      <c r="Z356" s="2" t="inlineStr"/>
+      <c r="AA356" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jared-higgitt-515a18194/</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Wholesalers Pty Ltd</t>
+        </is>
+      </c>
+      <c r="B357" s="2" t="inlineStr">
+        <is>
+          <t>Imperial Wholesalers Pty Ltd</t>
+        </is>
+      </c>
+      <c r="C357" s="2" t="inlineStr">
+        <is>
+          <t>47232</t>
+        </is>
+      </c>
+      <c r="D357" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E357" s="2" t="inlineStr">
+        <is>
+          <t>Brakpan</t>
+        </is>
+      </c>
+      <c r="F357" s="2" t="inlineStr">
+        <is>
+          <t>Gauteng, Ekurhuleni Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G357" s="2" t="inlineStr">
+        <is>
+          <t>60 Porter Street</t>
+        </is>
+      </c>
+      <c r="H357" s="2" t="inlineStr">
+        <is>
+          <t>1540</t>
+        </is>
+      </c>
+      <c r="I357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.imperialwholesalers.co.za</t>
+        </is>
+      </c>
+      <c r="J357" s="2" t="inlineStr"/>
+      <c r="K357" s="2" t="inlineStr"/>
+      <c r="L357" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="M357" s="2" t="inlineStr"/>
+      <c r="N357" s="2" t="inlineStr">
+        <is>
+          <t>info@imperialwholesalers.co.za</t>
+        </is>
+      </c>
+      <c r="O357" s="2" t="inlineStr">
+        <is>
+          <t>+27 11 740 6042</t>
+        </is>
+      </c>
+      <c r="P357" s="2" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="Q357" s="2" t="inlineStr">
+        <is>
+          <t>199202540623</t>
+        </is>
+      </c>
+      <c r="R357" s="2" t="inlineStr"/>
+      <c r="S357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/p/Imperial-Liquor-Wholesalers-PTY-LTD-61561611255856/</t>
+        </is>
+      </c>
+      <c r="T357" s="2" t="inlineStr"/>
+      <c r="U357" s="2" t="inlineStr"/>
+      <c r="V357" s="2" t="inlineStr"/>
+      <c r="W357" s="2" t="inlineStr">
+        <is>
+          <t>Jorge Costa</t>
+        </is>
+      </c>
+      <c r="X357" s="2" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="Y357" s="2" t="inlineStr"/>
+      <c r="Z357" s="2" t="inlineStr"/>
+      <c r="AA357" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/jorge-costa-b1511481</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B358" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C358" s="2" t="inlineStr">
+        <is>
+          <t>56825</t>
+        </is>
+      </c>
+      <c r="D358" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E358" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F358" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G358" s="2" t="inlineStr">
+        <is>
+          <t>11D Kloof Nek Road</t>
+        </is>
+      </c>
+      <c r="H358" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I358" s="2" t="inlineStr">
+        <is>
+          <t>https://publik.co.za</t>
+        </is>
+      </c>
+      <c r="J358" s="2" t="inlineStr"/>
+      <c r="K358" s="2" t="inlineStr"/>
+      <c r="L358" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M358" s="2" t="inlineStr"/>
+      <c r="N358" s="2" t="inlineStr">
+        <is>
+          <t>winebar@publik.co.za</t>
+        </is>
+      </c>
+      <c r="O358" s="2" t="inlineStr"/>
+      <c r="P358" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q358" s="2" t="inlineStr">
+        <is>
+          <t>201637149207</t>
+        </is>
+      </c>
+      <c r="R358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publik-wine/</t>
+        </is>
+      </c>
+      <c r="S358" s="2" t="inlineStr"/>
+      <c r="T358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/publikwine</t>
+        </is>
+      </c>
+      <c r="U358" s="2" t="inlineStr"/>
+      <c r="V358" s="2" t="inlineStr"/>
+      <c r="W358" s="2" t="inlineStr">
+        <is>
+          <t>Dominic Bodenstein</t>
+        </is>
+      </c>
+      <c r="X358" s="2" t="inlineStr">
+        <is>
+          <t>General Manager</t>
+        </is>
+      </c>
+      <c r="Y358" s="2" t="inlineStr"/>
+      <c r="Z358" s="2" t="inlineStr"/>
+      <c r="AA358" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/dominic-bodenstein-a31842272/</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="B359" s="2" t="inlineStr">
+        <is>
+          <t>Publik Distribution (pty) Ltd</t>
+        </is>
+      </c>
+      <c r="C359" s="2" t="inlineStr">
+        <is>
+          <t>56825</t>
+        </is>
+      </c>
+      <c r="D359" s="2" t="inlineStr">
+        <is>
+          <t>South Africa</t>
+        </is>
+      </c>
+      <c r="E359" s="2" t="inlineStr">
+        <is>
+          <t>Cape Town</t>
+        </is>
+      </c>
+      <c r="F359" s="2" t="inlineStr">
+        <is>
+          <t>Western Cape, City of Cape Town Metropolitan Municipality</t>
+        </is>
+      </c>
+      <c r="G359" s="2" t="inlineStr">
+        <is>
+          <t>11D Kloof Nek Road</t>
+        </is>
+      </c>
+      <c r="H359" s="2" t="inlineStr">
+        <is>
+          <t>8001</t>
+        </is>
+      </c>
+      <c r="I359" s="2" t="inlineStr">
+        <is>
+          <t>https://publik.co.za</t>
+        </is>
+      </c>
+      <c r="J359" s="2" t="inlineStr"/>
+      <c r="K359" s="2" t="inlineStr"/>
+      <c r="L359" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M359" s="2" t="inlineStr"/>
+      <c r="N359" s="2" t="inlineStr">
+        <is>
+          <t>winebar@publik.co.za</t>
+        </is>
+      </c>
+      <c r="O359" s="2" t="inlineStr"/>
+      <c r="P359" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q359" s="2" t="inlineStr">
+        <is>
+          <t>201637149207</t>
+        </is>
+      </c>
+      <c r="R359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/company/publik-wine/</t>
+        </is>
+      </c>
+      <c r="S359" s="2" t="inlineStr"/>
+      <c r="T359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/publikwine</t>
+        </is>
+      </c>
+      <c r="U359" s="2" t="inlineStr"/>
+      <c r="V359" s="2" t="inlineStr"/>
+      <c r="W359" s="2" t="inlineStr">
+        <is>
+          <t>Alex Greenleaf</t>
+        </is>
+      </c>
+      <c r="X359" s="2" t="inlineStr">
+        <is>
+          <t>Regional Manager</t>
+        </is>
+      </c>
+      <c r="Y359" s="2" t="inlineStr"/>
+      <c r="Z359" s="2" t="inlineStr"/>
+      <c r="AA359" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/alex-greenleaf-03072360/</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
